--- a/contenus/tab2/exs7-tcd-valeur-fournisseur.xlsx
+++ b/contenus/tab2/exs7-tcd-valeur-fournisseur.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consignes" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercice" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Correction" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1052,397 +1051,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Référence</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Fournisseur</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Valeur de stock (€)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>REF701</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>SecuEquip</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>REF702</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>SecuEquip</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>REF703</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>SecuEquip</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>REF704</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>SecuEquip</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>REF705</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>SecuEquip</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>REF706</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>SecuEquip</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>REF707</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>SecuEquip</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>REF708</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>LogiMat</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>REF709</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>LogiMat</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>REF710</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>LogiMat</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>2200</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>REF711</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>LogiMat</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>REF712</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>LogiMat</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>980</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>REF713</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>LogiMat</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>REF714</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>LogiMat</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>REF715</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>EmballagePro</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>REF716</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>EmballagePro</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>REF717</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>EmballagePro</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>REF718</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>EmballagePro</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>REF719</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>EmballagePro</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>REF720</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>EmballagePro</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>REF721</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>EmballagePro</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Fournisseur</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Valeur totale</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>SecuEquip</t>
-        </is>
-      </c>
-      <c r="B26">
-        <f>SUMIF(B2:B22,A26,C2:C22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>LogiMat</t>
-        </is>
-      </c>
-      <c r="B27">
-        <f>SUMIF(B2:B22,A27,C2:C22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>EmballagePro</t>
-        </is>
-      </c>
-      <c r="B28">
-        <f>SUMIF(B2:B22,A28,C2:C22)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>